--- a/EXECUTIVE_TEAM_AUDIT_REPORT_24_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_24_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -544,18 +544,36 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="B4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -572,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -628,7 +646,30 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -643,12 +684,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -664,6 +706,11 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
           <t>Grand Total</t>
         </is>
       </c>
@@ -677,21 +724,43 @@
       <c r="B2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C4" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -705,7 +774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX2"/>
+  <dimension ref="A1:AX3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -716,7 +785,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -1079,10 +1148,8 @@
           <t>PRAMOD YADAV</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9851202417</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9851202417</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -1172,10 +1239,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
@@ -1186,37 +1251,253 @@
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS2" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT2" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 16m</t>
+        </is>
+      </c>
+      <c r="AU2" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV2" s="3" t="inlineStr">
+        <is>
           <t>Case : IPTV remote  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS2" s="3" t="inlineStr">
+      <c r="AW2" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX2" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 11:57 AM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>TKT1376631</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Raut</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Raut</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>9861569905</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 11:57:25 AM</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>9861569905</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 12:21:09 PM</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 11:57:25 AM</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>27.657741</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>Unnamed Road, M958+5CJ, Mahalaxmi 44600, Near by Shree Jana Sneha Krishi Bahu Udesya Sahakari Sansth</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>rautnirajan306@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>09:36 hour</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Sagar Khadka</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>L27-6</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>85.366226</t>
+        </is>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT2" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 16m</t>
-        </is>
-      </c>
-      <c r="AU2" s="3" t="inlineStr">
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>23h 36m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV2" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV remote  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW2" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
-        </is>
-      </c>
-      <c r="AX2" s="3" t="inlineStr">
-        <is>
-          <t>Chandramani Tharu</t>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_24_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_24_Oct_2026.xlsx
@@ -820,7 +820,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1352,10 +1352,8 @@
           <t>Nirajan Raut</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9861569905</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9861569905</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1390,10 +1388,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>27.657741</t>
-        </is>
+      <c r="Y3" s="3" t="n">
+        <v>27.657741</v>
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
@@ -1449,25 +1445,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>L27-6</t>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>85.366226</t>
-        </is>
+      <c r="AP3" s="3" t="n">
+        <v>85.366226</v>
       </c>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_24_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_24_Oct_2026.xlsx
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -568,10 +568,10 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
@@ -590,10 +590,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -630,7 +630,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>IPTV Issue</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -646,14 +646,14 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>WiFi 6 Upgrade</t>
+          <t>IPTV Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -669,7 +669,30 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -718,30 +741,30 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="D3" s="6" t="n">
         <v>1</v>
@@ -757,10 +780,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -774,7 +797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX3"/>
+  <dimension ref="A1:AX4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -785,7 +808,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -814,18 +837,18 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="15" customWidth="1" min="38" max="38"/>
+    <col width="22" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
-    <col width="20" customWidth="1" min="49" max="49"/>
+    <col width="25" customWidth="1" min="49" max="49"/>
     <col width="20" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
@@ -1493,6 +1516,214 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 12:36 PM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi - 6 Router Instal  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Wifi - 6 Router Instal</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1376706</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Ashok tamang</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Ashok tamang</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9865115046</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 12:36:01 PM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>BKT9865115046</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 02:17:45 PM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 12:36:01 PM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Lokenthali 3 kune, Bhaktapur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>9865115046@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>08:19 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Rajnikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>L36-3</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi - 6 Router Instal  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>22h 18m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi - 6 Router Instal  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_24_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_24_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -562,18 +562,36 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="B5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -634,10 +652,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -646,7 +664,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -669,7 +687,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -692,7 +710,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -707,13 +725,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -734,6 +753,11 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>Grand Total</t>
         </is>
       </c>
@@ -750,7 +774,10 @@
       <c r="C2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="6" t="n">
         <v>2</v>
       </c>
     </row>
@@ -766,24 +793,49 @@
       <c r="C3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="4" t="n">
-        <v>3</v>
+      <c r="D5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -797,7 +849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX4"/>
+  <dimension ref="A1:AX5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -810,10 +862,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -827,12 +879,12 @@
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
     <col width="29" customWidth="1" min="32" max="32"/>
-    <col width="27" customWidth="1" min="33" max="33"/>
+    <col width="30" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -1583,10 +1635,8 @@
           <t>Ashok tamang</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9865115046</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9865115046</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1676,10 +1726,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
@@ -1690,29 +1738,29 @@
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>22h 18m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi - 6 Router Instal  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS4" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT4" s="3" t="inlineStr">
-        <is>
-          <t>22h 18m</t>
-        </is>
-      </c>
-      <c r="AU4" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV4" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi - 6 Router Instal  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
       <c r="AW4" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -1721,6 +1769,222 @@
       <c r="AX4" s="3" t="inlineStr">
         <is>
           <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 12:44 PM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>no light blinking</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1376730</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Binir Kayastha Shrestha</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Binir Kayastha Shrestha</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9841519997</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 03:14:20 PM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9841519997</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 03:09:37 PM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 12:44:37 PM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>27.720628</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>RB Inn - Hotel Nagarjun 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>awesomeland0132@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>07:35 hour</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Pramila Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>CDB428</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>85.279862</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>21h 30m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>21h 35m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_24_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_24_Oct_2026.xlsx
@@ -895,7 +895,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1839,10 +1839,8 @@
           <t>Binir Kayastha Shrestha</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9841519997</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9841519997</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1877,10 +1875,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>27.720628</t>
-        </is>
+      <c r="Y5" s="3" t="n">
+        <v>27.720628</v>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
@@ -1936,25 +1932,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>CDB428</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.279862</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>85.27986199999999</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : no light blinking  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_24_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_24_Oct_2026.xlsx
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -675,10 +675,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -803,39 +803,58 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="4" t="n">
+      <c r="C6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="4" t="n">
-        <v>4</v>
+      <c r="E6" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -849,7 +868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX5"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -878,7 +897,7 @@
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
@@ -895,7 +914,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1980,6 +1999,222 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 1:22 PM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV not working   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV not working</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1373677</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Shrestha</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Shrestha</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9851013189</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 01:22:54 PM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9851013189</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 02:25:13 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 01:22:54 PM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>27.65171</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-customer care</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>New Millennium School,J8XX+M2V, Mahalaxmi , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>shrestha143nisha@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>10:57 hour</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr"/>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>2,7</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>85.34641</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV not working   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>6d 22h 57m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV not working   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_24_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_24_Oct_2026.xlsx
@@ -568,10 +568,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -725,10 +725,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -822,7 +822,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Low Wi-Fi Range on both band</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -839,22 +839,41 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>5</v>
+      <c r="D7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -868,7 +887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX6"/>
+  <dimension ref="A1:AX7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -903,7 +922,7 @@
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
     <col width="29" customWidth="1" min="32" max="32"/>
-    <col width="30" customWidth="1" min="33" max="33"/>
+    <col width="31" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -2066,10 +2085,8 @@
           <t>Nisha Shrestha</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9851013189</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9851013189</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -2104,10 +2121,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>27.65171</t>
-        </is>
+      <c r="Y6" s="3" t="n">
+        <v>27.65171</v>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
@@ -2163,47 +2178,43 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>2,7</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>85.34641</t>
-        </is>
+      <c r="AP6" s="3" t="n">
+        <v>85.34641000000001</v>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>6d 22h 57m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
           <t>Case : IPTV not working   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS6" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT6" s="3" t="inlineStr">
-        <is>
-          <t>6d 22h 57m</t>
-        </is>
-      </c>
-      <c r="AU6" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV6" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV not working   has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
       <c r="AW6" s="3" t="inlineStr">
         <is>
           <t>IPTV Issue</t>
@@ -2212,6 +2223,214 @@
       <c r="AX6" s="3" t="inlineStr">
         <is>
           <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 1:34 PM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi  range   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>wifi  range</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1376810</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Sonim Manandhar</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Sonim Manandhar</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9702616130</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 05:36:42 PM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>KLK9702616130</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 05:29:23 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 01:34:40 PM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Chamati Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>9702616130@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on both band</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>06:05 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Bashu Bhat</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>CDB313</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr"/>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi  range   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>19h 57m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>20h 5m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi  range   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_24_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_24_Oct_2026.xlsx
@@ -933,7 +933,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -2293,10 +2293,8 @@
           <t>Sonim Manandhar</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9702616130</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9702616130</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -2386,10 +2384,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
@@ -2400,7 +2396,7 @@
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi  range   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_24_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_24_Oct_2026.xlsx
@@ -568,10 +568,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
@@ -675,10 +675,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -841,7 +841,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>NETTV-Blank TV Display</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -858,22 +858,41 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>6</v>
+      <c r="D8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -887,7 +906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX7"/>
+  <dimension ref="A1:AX9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -933,7 +952,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -2430,6 +2449,430 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 2:06 PM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377162</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Jyoti Sharma</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Jyoti Sharma</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9841221094</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 11:47:54 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>KLK9841221094</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 11:34:32 AM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 02:06:12 PM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr"/>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>27.71028449462496, 85.29539256891584, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>9841768213@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>02:31 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Salbin Ghale</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>CDB451</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr"/>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>2h 18m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>2h 31m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 2:05 PM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377162</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Jyoti Sharma</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Jyoti Sharma</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9841221094</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 11:47:54 AM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>KLK9841221094</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 11:34:32 AM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 02:06:12 PM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>27.71028449462496, 85.29539256891584, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>9841768213@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>02:31 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Salbin Ghale</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>CDB451</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>2h 18m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>2h 31m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_24_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_24_Oct_2026.xlsx
@@ -952,7 +952,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -2516,10 +2516,8 @@
           <t>Jyoti Sharma</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9841221094</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9841221094</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2591,10 +2589,8 @@
           <t>NETTV-Blank TV Display</t>
         </is>
       </c>
-      <c r="AH8" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH8" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI8" s="3" t="inlineStr">
         <is>
@@ -2613,10 +2609,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
@@ -2627,7 +2621,7 @@
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -2728,10 +2722,8 @@
           <t>Jyoti Sharma</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9841221094</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9841221094</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2803,10 +2795,8 @@
           <t>NETTV-Blank TV Display</t>
         </is>
       </c>
-      <c r="AH9" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH9" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI9" s="3" t="inlineStr">
         <is>
@@ -2825,10 +2815,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
@@ -2839,7 +2827,7 @@
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_24_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_24_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>8</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -803,14 +803,14 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Fiber wire breakage suspect</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0</v>
@@ -822,17 +822,17 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on both band</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>1</v>
@@ -841,7 +841,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Blank TV Display</t>
+          <t>Low Wi-Fi Range on both band</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -860,7 +860,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>NETTV-Blank TV Display</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -877,22 +877,41 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="4" t="n">
+      <c r="B9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E8" s="4" t="n">
-        <v>7</v>
+      <c r="E9" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -906,7 +925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX9"/>
+  <dimension ref="A1:AX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -920,7 +939,7 @@
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="26" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
@@ -944,18 +963,18 @@
     <col width="31" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
-    <col width="17" customWidth="1" min="36" max="36"/>
+    <col width="26" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="22" customWidth="1" min="38" max="38"/>
-    <col width="20" customWidth="1" min="39" max="39"/>
+    <col width="21" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="24" customWidth="1" min="47" max="47"/>
+    <col width="36" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
     <col width="20" customWidth="1" min="50" max="50"/>
@@ -2861,6 +2880,234 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 2:56 PM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : router faulty   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>router faulty</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1376956</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Pathak</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Pathak</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9841495050</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 02:59:32 PM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 11: 15:00 AM</t>
+        </is>
+      </c>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9841495050</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 07:15:29 AM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 02:59:32 PM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>27.663273</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>Hari Rijal</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Thimi-Biruwa Rd, Anantalingeshwar Near By Harsha Chowk, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>nirajanphk@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Fiber wire breakage suspect</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>04:56 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr">
+        <is>
+          <t>19:04 hour / 00:00 hour</t>
+        </is>
+      </c>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Bhawana Bista</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>MS TICKET  HANDLER</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>L15-3</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>85.392718</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : router faulty   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>7h 44m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : router faulty   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX10" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_24_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_24_Oct_2026.xlsx
@@ -971,7 +971,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2947,10 +2947,8 @@
           <t>Nirajan Pathak</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9841495050</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9841495050</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2989,10 +2987,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>27.663273</t>
-        </is>
+      <c r="Y10" s="3" t="n">
+        <v>27.663273</v>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
@@ -3030,10 +3026,8 @@
           <t>Fiber wire breakage suspect</t>
         </is>
       </c>
-      <c r="AH10" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH10" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI10" s="3" t="inlineStr">
         <is>
@@ -3056,25 +3050,21 @@
           <t>MS TICKET  HANDLER</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>L15-3</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>85.392718</t>
-        </is>
+      <c r="AP10" s="3" t="n">
+        <v>85.392718</v>
       </c>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : router faulty   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_24_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_24_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>8</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>36.4%</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>36.4%</t>
         </is>
       </c>
     </row>
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>27.3%</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>2</v>
@@ -778,17 +778,17 @@
         <v>0</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Fiber wire breakage suspect</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
@@ -797,13 +797,13 @@
         <v>0</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Fiber wire breakage suspect</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>3</v>
@@ -911,7 +911,7 @@
         <v>3</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -925,7 +925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX10"/>
+  <dimension ref="A1:AX12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -971,7 +971,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -3098,6 +3098,438 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 4:01 PM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377020</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Ranju Nepali</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Ranju Nepali</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9813475180</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 09:04:28 AM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>9880534715</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 09:04:28 AM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 04:01:57 PM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>Glacier International School (school block) - Middle school M8QV+Q39 Thulo Kharibot Marga Kathmandu</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>ranjunepali432@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr"/>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>L22-5</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr"/>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>6h 57m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>6h 57m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 3:56 PM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377270</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Pragal Kc</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Pragal Kc</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9841915176</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 03:59:14 PM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 05: 03:00 PM</t>
+        </is>
+      </c>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9841915176</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 01:03:33 PM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 03:59:14 PM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.669</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>Hari Rijal</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Sisha Cafe With Fast Food,Ekatamarga 34, ???????? , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>pragalrock@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Fiber wire breakage suspect</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>02:53 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr">
+        <is>
+          <t>21:07 hour / 00:00 hour</t>
+        </is>
+      </c>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>MS TICKET  HANDLER</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>L24-7</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.34123</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>2h 55m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX12" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_24_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_24_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>8</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>33.3%</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>27.3%</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>2</v>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>3</v>
@@ -911,7 +911,7 @@
         <v>3</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -925,7 +925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX12"/>
+  <dimension ref="A1:AX13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3165,10 +3165,8 @@
           <t>Ranju Nepali</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9813475180</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9813475180</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -3254,10 +3252,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
@@ -3268,7 +3264,7 @@
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
@@ -3369,10 +3365,8 @@
           <t>Pragal Kc</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9841915176</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9841915176</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -3411,10 +3405,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.669</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.669</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -3452,10 +3444,8 @@
           <t>Fiber wire breakage suspect</t>
         </is>
       </c>
-      <c r="AH12" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH12" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI12" s="3" t="inlineStr">
         <is>
@@ -3478,53 +3468,253 @@
           <t>MS TICKET  HANDLER</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>L24-7</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.34123</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.34123</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>2h 55m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS12" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT12" s="3" t="inlineStr">
-        <is>
-          <t>2h 55m</t>
-        </is>
-      </c>
-      <c r="AU12" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (In Progress)</t>
-        </is>
-      </c>
-      <c r="AV12" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW12" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
       <c r="AX12" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 4:03 PM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377006</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Aakriti Bhandari</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Aakriti Bhandari</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9847902722</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 08:46:06 AM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>9847902722</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 08:46:06 AM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 04:03:45 PM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr"/>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>Maitidevi chowk , birendra marga, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>bhandaryaakriti9@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr"/>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>CDB164</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr"/>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>7h 17m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>7h 17m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX13" s="3" t="inlineStr">
         <is>
           <t>Chandramani Tharu</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_24_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_24_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.8%</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.8%</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -803,14 +803,14 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0</v>
@@ -822,14 +822,14 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
@@ -896,22 +896,41 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C9" s="4" t="n">
+      <c r="B10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D10" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="4" t="n">
-        <v>11</v>
+      <c r="E10" s="4" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -925,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX13"/>
+  <dimension ref="A1:AX14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -938,10 +957,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="27" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="27" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -3583,10 +3602,8 @@
           <t>Aakriti Bhandari</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9847902722</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9847902722</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3672,10 +3689,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
@@ -3686,35 +3701,243 @@
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>7h 17m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>7h 17m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
           <t>Case : Wi-Fi 6   has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS13" s="3" t="inlineStr">
-        <is>
-          <t>7h 17m</t>
-        </is>
-      </c>
-      <c r="AT13" s="3" t="inlineStr">
-        <is>
-          <t>7h 17m</t>
-        </is>
-      </c>
-      <c r="AU13" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV13" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW13" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
       <c r="AX13" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 4:31 PM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light on the router  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>no light on the router</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377051</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Chandra Bahadur shrestha</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Chandra Bahadur shrestha</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9841598179</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 04:31:45 PM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9841598179</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 09:47:23 AM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 04:31:45 PM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr"/>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>near by Mahalaxmi Party Venue - Banquet hall, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr">
+        <is>
+          <t>birenshrestha.bs@gmail.co</t>
+        </is>
+      </c>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>06:31 hour</t>
+        </is>
+      </c>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>CDB931</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr"/>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light on the router  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>6h 44m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light on the router  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX14" s="3" t="inlineStr">
         <is>
           <t>Chandramani Tharu</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_24_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_24_Oct_2026.xlsx
@@ -990,7 +990,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -3802,10 +3802,8 @@
           <t>Chandra Bahadur shrestha</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9841598179</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9841598179</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3895,10 +3893,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
@@ -3909,7 +3905,7 @@
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : no light on the router  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
